--- a/data/live/MASTER_NEWS_DATA.xlsx
+++ b/data/live/MASTER_NEWS_DATA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I141"/>
+  <dimension ref="A1:I164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3051,17 +3051,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-21 04:26</t>
+          <t>2026-08-21 07:47</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>News Website</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>The Sentinel Assam</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assam: Draft Electoral Roll Published for 35-Dihing Sessa Constituency </t>
+          <t>Binance Donates INR 3.3 Crore to Goonj's Rahat Initiative for Assam Flood Relief - PR Newswire &lt;a href="https://news.google.com/rss/articles/CBMi1AFBVV95cUxNNmVyQTNQcnZpNTc1aGdUSmNNM0JBVDdOVjFFSGdkR2lhVmRnbmphRS0tVER4UjdUeS0tU0UtT0ZxeG5aWEdsRFZ0R2RMZmQwQ3pTb1NtNVluMnUzVG5WcXR0Y3lrdk5PZ0tOMEpBR1RiQ0lhZjAyby12U013SjJyYU84WTZTUjBBR3M0ZERhb1hjR01sUFQ4SWFLZnU3NHdkT25BcmN2V2cxM1pQRE5JemctbWJsVGxUSC1kVzJRRDNoSC1uZ24wVFB1a1NGcF8wNy1saw?oc=5" target="_blank"&gt;Binance Donates INR 3.3 Crore to Goonj's Rahat</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3081,44 +3081,44 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/assam-draft-electoral-roll-published-for-35-dihing-sessa-constituency</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNNmVyQTNQcnZpNTc1aGdUSmNNM0JBVDdOVjFFSGdkR2lhVmRnbmphRS0tVER4UjdUeS0tU0UtT0ZxeG5aWEdsRFZ0R2RMZmQwQ3pTb1NtNVluMnUzVG5WcXR0Y3lrdk5PZ0tOMEpBR1RiQ0lhZjAyby12U013SjJyYU84WTZTUjBBR3M0ZERhb1hjR01sUFQ4SWFLZnU3NHdkT25BcmN2V2cxM1pQRE5JemctbWJsVGxUSC1kVzJRRDNoSC1uZ24wVFB1a1NGcF8wNy1saw?oc=5</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 13:33</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-21 04:23</t>
+          <t>2026-08-21 07:12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>News Website</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The Sentinel Assam</t>
+          <t>The News Mill</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Assam (General)</t>
+          <t>Jorhat</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meghalaya Dy CM Dhar Calls for Peace, Dialogue as Meghalaya-Assam Tensions Continue </t>
+          <t>Nine families in Jorhat displaced over a month after Assam floods - The News Mill &lt;a href="https://news.google.com/rss/articles/CBMinwFBVV95cUxObU1ZYTFudnp3QjFnYVFiQVVBdHZtd3NEWWxWUnNSdThPanlWYnRMdEgyaGRxVGFJTTdUbDQyNGY0ZU1NZkMyQ2I5NmhEUDQ2ZnVBWFgtVkU2ZWVIOG8zTEZ5TG05VW9fZHB4YUdxSmVvYjVKSjZMTlhkVm16Z3RvVjRPbnFZWER2bThMQ0c4SjI5UUVkT2xZXzBBbF9sMEE?oc=5" target="_blank"&gt;Nine families in Jorhat displaced over a month after Assam floods&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;The News Mill&lt;/font&gt;</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3128,44 +3128,44 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/meghalaya-news/meghalaya-dy-cm-dhar-calls-for-peace-dialogue-as-meghalaya-assam-tensions-continue</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxObU1ZYTFudnp3QjFnYVFiQVVBdHZtd3NEWWxWUnNSdThPanlWYnRMdEgyaGRxVGFJTTdUbDQyNGY0ZU1NZkMyQ2I5NmhEUDQ2ZnVBWFgtVkU2ZWVIOG8zTEZ5TG05VW9fZHB4YUdxSmVvYjVKSjZMTlhkVm16Z3RvVjRPbnFZWER2bThMQ0c4SjI5UUVkT2xZXzBBbF9sMEE?oc=5</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 13:33</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-21 04:22</t>
+          <t>2026-08-21 07:17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>News Website</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>The Sentinel Assam</t>
+          <t>Prag News</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Kamrup Metro</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panbazar Police Arrest Three, Recover Stolen Scooty and Gold in Guwahati Theft Case </t>
+          <t>Gaurav Gogoi Urges ₹10,000 Cr Flood Relief for Assam, Questions PM CARES Fund - Prag News &lt;a href="https://news.google.com/rss/articles/CBMiogFBVV95cUxOaTZ0QzZNN19FMXVSWExUWHNFNm9iWWhNSnhpM2xjeURjdVM3eldFNWtpclFDdTRpRVVIY1FZNXVRUHk0S21hc3VlaHQzUEZkMkpuNnpCendIWjRXYkFjYjk4enI0bEJUdlFGWllEem9LT1FJMFFmd3J0eV8zWGxxS1NtWlV2d3dzT2ppWWpGWHA3eDFmRkRWMHdyV1lJT0N1enc?oc=5" target="_blank"&gt;Gaurav Gogoi Urges ₹10,000 Cr Flood Relief for Assam, Questions PM CARES Fund&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Pra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3175,44 +3175,44 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/cities/guwahati-city/panbazar-police-arrest-three-recover-stolen-scooty-and-gold-in-guwahati-theft-case</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOaTZ0QzZNN19FMXVSWExUWHNFNm9iWWhNSnhpM2xjeURjdVM3eldFNWtpclFDdTRpRVVIY1FZNXVRUHk0S21hc3VlaHQzUEZkMkpuNnpCendIWjRXYkFjYjk4enI0bEJUdlFGWllEem9LT1FJMFFmd3J0eV8zWGxxS1NtWlV2d3dzT2ppWWpGWHA3eDFmRkRWMHdyV1lJT0N1enc?oc=5</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 13:33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-21 04:18</t>
+          <t>2026-08-21 05:05</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>News Website</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The Sentinel Assam</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Dibrugarh</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assam: Dibrugarh District Primary Teachers’ Association Extends Aid to Flood-Affected Schools </t>
+          <t>Assam CM Himanta Biswa Sarma calls on PM Modi, discusses state flood recovery and development agenda - The Economic Times &lt;a href="https://news.google.com/rss/articles/CBMiigJBVV95cUxNbW1GX09Qb1BiY1FYRG5iZjNUbFNwN3dWTmJ1ZUJZYWNNRWtyTEpvZzZKdEpibVBFWjNvY0VJZ1U1UmdyalBrUXVDaVNlS2RwWF9ycWdfakhhU1hGTGZCZ09DNnlOZnhrSWx0amlXenZfOThTV1lEZllGYm1QVUhkWnJJU3ptVmoxd3RKd3ZZek1RSTlGWVVtRk8xUUlYZlRnMXBkNkk1Z1MyT19DVm1CVGE3WWhSb1lVWGFIN2dVTjZnRktDVUdHWUxfTzFlWmliNkJDNzRYRGw3ZHJBTEFCS2hYTFRjampESWc3ai1PT1hpdlpv</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3227,29 +3227,29 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/assam-dibrugarh-district-primary-teachers-association-extends-aid-to-flood-affected-schools</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNbW1GX09Qb1BiY1FYRG5iZjNUbFNwN3dWTmJ1ZUJZYWNNRWtyTEpvZzZKdEpibVBFWjNvY0VJZ1U1UmdyalBrUXVDaVNlS2RwWF9ycWdfakhhU1hGTGZCZ09DNnlOZnhrSWx0amlXenZfOThTV1lEZllGYm1QVUhkWnJJU3ptVmoxd3RKd3ZZek1RSTlGWVVtRk8xUUlYZlRnMXBkNkk1Z1MyT19DVm1CVGE3WWhSb1lVWGFIN2dVTjZnRktDVUdHWUxfTzFlWmliNkJDNzRYRGw3ZHJBTEFCS2hYTFRjampESWc3ai1PT1hpdlpva0xRemZZSGMwVVF4ZnZRT29ua3NxZ9IBjwJBVV95cUxNQy16NUlUTF8wN2FLM0QzaE53N0VlOW9wZjF3ZTBYT0JwajBSaW8ySUZZM1FvcVN2YVdQWVlPYkNucVBPaEFTVXFqRnJDT21pOHBFRDF5cVZlQ1JwVVFzWlg4YnJuMDZNd1o5Q0xuQ0FJUzRZLTRYU0V5a2ZGWURaTlMwY2RnVUEwT0ROMDhBUGU2cy11NW5DaUtocW4ySTlvbDlPNjRHWHhhTmpkLXJGMk1kQVJtNUc0V2ZoVkx0WHppVW9QdTRyeFRJdlFWdncyRW9yOUs4T2czUlhHXzJsN29KYVdjWGVnZFY3Z0NvZjJLVXF0dFFlUnUtM0xoUnRtaDM1emV5amJ1RXdIZlhv?oc=5</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 13:33</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-21 04:16</t>
+          <t>2026-08-21 07:02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>News Website</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>The Sentinel Assam</t>
+          <t>The Assam Tribune</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assam: AGP leader urges review of proposed Rakhyasini reserve forest boundary </t>
+          <t>Assam-Meghalaya traffic hit as Jorabat blockade enters second day - The Assam Tribune &lt;a href="https://news.google.com/rss/articles/CBMipwFBVV95cUxNS1JuTlFlVE1ndmZlQzBkVTZ0MEJnMXpzTzZIV3FLbDFka0ZfYk9NeHVlbWdqeVp2QWtxWEczZjJCbjN3a0lJZVZ0REZtazRMeHFyTzd1SER5VW5scmg2QW50ajNBOFJjbmhIS2xjdnVRZko0R1V6cUxsak9PNnVpbDh1S21qckloOHJ5ZmJjaW1xdlhCX09mZ2JMY0lJYWViWENXNWgxd9IBrAFBVV95cUxPQ3d5cTFwN3BpOE1QUERKdWxzOXRNY2MwWFllMkZQRFd5ZXdOVzZEVm13UUdkXzZRc3FxN3VOQ25GemMwd25HTWw3R3drenFNYTR0bU1pNmZzMnJwWlVmcHJ2S2FW</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3269,44 +3269,44 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/assam-agp-leader-urges-review-of-proposed-rakhyasini-reserve-forest-boundary</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNS1JuTlFlVE1ndmZlQzBkVTZ0MEJnMXpzTzZIV3FLbDFka0ZfYk9NeHVlbWdqeVp2QWtxWEczZjJCbjN3a0lJZVZ0REZtazRMeHFyTzd1SER5VW5scmg2QW50ajNBOFJjbmhIS2xjdnVRZko0R1V6cUxsak9PNnVpbDh1S21qckloOHJ5ZmJjaW1xdlhCX09mZ2JMY0lJYWViWENXNWgxd9IBrAFBVV95cUxPQ3d5cTFwN3BpOE1QUERKdWxzOXRNY2MwWFllMkZQRFd5ZXdOVzZEVm13UUdkXzZRc3FxN3VOQ25GemMwd25HTWw3R3drenFNYTR0bU1pNmZzMnJwWlVmcHJ2S2FWTy1ZYzFBV3BkTDhmc0NvSkRvYWIzVUs0UC0zOVZQVWpfOGkzZ0EzcVRtcXlFUDcwVzd2Q2ZuODcxMUlqSFYydWhQZnhrcmRa?oc=5</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 13:33</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-21 04:08</t>
+          <t>2026-08-21 07:04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>News Website</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>The Sentinel Assam</t>
+          <t>The Assam Tribune</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Kamrup Metro</t>
+          <t>Biswanath</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two drug peddlers arrested with heroin in Guwahati </t>
+          <t>Biswanath fisherfolk express support for ESZ reduction, criticize Gaurav Gogoi - The Assam Tribune &lt;a href="https://news.google.com/rss/articles/CBMipAFBVV95cUxNcnd3X0pzelQ5WWxxT1NHb3NONmZGZGhTOGRJdkhyVU9SUk15Wmxvdkgtd2pUVWUxbkRXS0w4RnFUQVFnaDFicWlUdnpQdHQ4VGZqOWpScmVYRWZIYjdJU1dtLThsdlBqck9pdW1ZMFNBTEZ5cmowZVRaendvcFJmSWZJU1plcGZqLUhfbTBla1U5aHh3SlNmWUs1azFqaFM3cmNBMtIBqgFBVV95cUxNTW9tejhMZ2t5bGVfa2VFTTZueWlLcDlNMkxhQk5GLWFyVTF6WHc5UmtoRkpYc05jTm5qU2p6YUx3YnFQekJrdkViSFpRWEJCd181TUd4VGFpWWJLVzF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3316,44 +3316,44 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/cities/guwahati-city/two-drug-peddlers-arrested-with-heroin-in-guwahati</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNcnd3X0pzelQ5WWxxT1NHb3NONmZGZGhTOGRJdkhyVU9SUk15Wmxvdkgtd2pUVWUxbkRXS0w4RnFUQVFnaDFicWlUdnpQdHQ4VGZqOWpScmVYRWZIYjdJU1dtLThsdlBqck9pdW1ZMFNBTEZ5cmowZVRaendvcFJmSWZJU1plcGZqLUhfbTBla1U5aHh3SlNmWUs1azFqaFM3cmNBMtIBqgFBVV95cUxNTW9tejhMZ2t5bGVfa2VFTTZueWlLcDlNMkxhQk5GLWFyVTF6WHc5UmtoRkpYc05jTm5qU2p6YUx3YnFQekJrdkViSFpRWEJCd181TUd4VGFpWWJLVzFhVXdFNHliUGMxOTh1ajhPbEhjcEl3Z29TWHpkRXlxb0J2M3NIWVg1cFR6WXFfdldHWmVmYjJzUFhhLXp0MXdjUjdsMzFJMTgteG5tZw?oc=5</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 13:33</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-21 04:05</t>
+          <t>2026-08-21 07:29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>News Website</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>The Sentinel Assam</t>
+          <t>Brighter Kashmir</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Kamrup Metro</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Speeding Vehicle Crashes into Six-Mile Flyover in Guwahati </t>
+          <t>Assam Rifles brings medical aid to flood-hit communities - Brighter Kashmir &lt;a href="https://news.google.com/rss/articles/CBMiogFBVV95cUxNOEZ3Rjl2Rm1qVEJONHJmMklkcDJWMDJSTFJlLTFwV2h0ZUZSc2F3MXRhYTZvX1V3VjQ5ZklwTmN5V1MxTDFGRmZ3ek9IQVlDbmxWOVZ3ZFkwS201OHlTNzNhRE9qdDEteXI3QVpjVnQtUlJZNk9pNDJqOXM0azY1d3cySUpXenAxRFdYYy10VTBVS0FNamhYaTdfOFE4cm1RZHc?oc=5" target="_blank"&gt;Assam Rifles brings medical aid to flood-hit communities&lt;/a&gt;&amp;nbsp;&amp;nbsp;&lt;font color="#6f6f6f"&gt;Brighter Kashmir&lt;/font&gt;</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3363,24 +3363,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/cities/guwahati-city/speeding-vehicle-crashes-into-six-mile-flyover-in-guwahati</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNOEZ3Rjl2Rm1qVEJONHJmMklkcDJWMDJSTFJlLTFwV2h0ZUZSc2F3MXRhYTZvX1V3VjQ5ZklwTmN5V1MxTDFGRmZ3ek9IQVlDbmxWOVZ3ZFkwS201OHlTNzNhRE9qdDEteXI3QVpjVnQtUlJZNk9pNDJqOXM0azY1d3cySUpXenAxRFdYYy10VTBVS0FNamhYaTdfOFE4cm1RZHc?oc=5</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 13:33</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-21 03:58</t>
+          <t>2026-08-21 04:26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Kamrup Metro</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assam Congress marks Rajiv Gandhi’s 82nd birth anniversary with tributes in Guwahati </t>
+          <t xml:space="preserve">Assam: Draft Electoral Roll Published for 35-Dihing Sessa Constituency </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/cities/guwahati-city/assam-congress-marks-rajiv-gandhis-82nd-birth-anniversary-with-tributes-in-guwahati</t>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/assam-draft-electoral-roll-published-for-35-dihing-sessa-constituency</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3427,7 +3427,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-21 03:55</t>
+          <t>2026-08-21 04:23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assam’s Indigenous ‘Asomi’ Sheep Breed Secures National Recognition from ICAR-NBAGR </t>
+          <t xml:space="preserve">Meghalaya Dy CM Dhar Calls for Peace, Dialogue as Meghalaya-Assam Tensions Continue </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/topheadlines/assams-indigenous-asomi-sheep-breed-secures-national-recognition-from-icar-nbagr</t>
+          <t>https://www.sentinelassam.com/north-east-india-news/meghalaya-news/meghalaya-dy-cm-dhar-calls-for-peace-dialogue-as-meghalaya-assam-tensions-continue</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3474,7 +3474,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-21 03:54</t>
+          <t>2026-08-21 04:22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guwahati: Two cops injured as dispute over land of ex-CM Mahanta turns violent; 8 held </t>
+          <t xml:space="preserve">Panbazar Police Arrest Three, Recover Stolen Scooty and Gold in Guwahati Theft Case </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/cities/guwahati-city/guwahati-two-cops-injured-as-dispute-over-land-of-ex-cm-mahanta-turns-violent-8-held</t>
+          <t>https://www.sentinelassam.com/cities/guwahati-city/panbazar-police-arrest-three-recover-stolen-scooty-and-gold-in-guwahati-theft-case</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-21 03:51</t>
+          <t>2026-08-21 04:18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Kamrup Metro</t>
+          <t>Dibrugarh</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDRF rescues 57-year-old woman from Brahmaputra in Guwahati </t>
+          <t xml:space="preserve">Assam: Dibrugarh District Primary Teachers’ Association Extends Aid to Flood-Affected Schools </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/cities/guwahati-city/ndrf-rescues-57-year-old-woman-from-brahmaputra-in-guwahati</t>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/assam-dibrugarh-district-primary-teachers-association-extends-aid-to-flood-affected-schools</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3568,7 +3568,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-21 03:40</t>
+          <t>2026-08-21 04:16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assam Government tightens rules for suspended employees </t>
+          <t xml:space="preserve">Assam: AGP leader urges review of proposed Rakhyasini reserve forest boundary </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/topheadlines/assam-government-tightens-rules-for-suspended-employees</t>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/assam-agp-leader-urges-review-of-proposed-rakhyasini-reserve-forest-boundary</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3615,7 +3615,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-21 03:34</t>
+          <t>2026-08-21 04:08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Assam (General)</t>
+          <t>Kamrup Metro</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">PM Modi Assures Unwavering Support as Assam CM Sarma Discusses Flood and Development Roadmap </t>
+          <t xml:space="preserve">Two drug peddlers arrested with heroin in Guwahati </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Flood</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/topheadlines/pm-modi-assures-unwavering-support-as-assam-cm-sarma-discusses-flood-and-development-roadmap</t>
+          <t>https://www.sentinelassam.com/cities/guwahati-city/two-drug-peddlers-arrested-with-heroin-in-guwahati</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3662,7 +3662,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-21 03:29</t>
+          <t>2026-08-21 04:05</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Assam (General)</t>
+          <t>Kamrup Metro</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meghalaya CM Sangma Holds Talks With Assam Counterpart to Restore Normalcy </t>
+          <t xml:space="preserve">Speeding Vehicle Crashes into Six-Mile Flyover in Guwahati </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/topheadlines/meghalaya-cm-sangma-holds-talks-with-assam-counterpart-to-restore-normalcy</t>
+          <t>https://www.sentinelassam.com/cities/guwahati-city/speeding-vehicle-crashes-into-six-mile-flyover-in-guwahati</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3709,7 +3709,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-21 03:24</t>
+          <t>2026-08-21 03:58</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Assam (General)</t>
+          <t>Kamrup Metro</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assam-Meghalaya border tense at Jorabat amid blockade over alleged attacks on vehicles </t>
+          <t xml:space="preserve">Assam Congress marks Rajiv Gandhi’s 82nd birth anniversary with tributes in Guwahati </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/topheadlines/assam-meghalaya-border-tense-at-jorabat-amid-blockade-over-alleged-attacks-on-vehicles</t>
+          <t>https://www.sentinelassam.com/cities/guwahati-city/assam-congress-marks-rajiv-gandhis-82nd-birth-anniversary-with-tributes-in-guwahati</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3756,7 +3756,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-21 03:19</t>
+          <t>2026-08-21 03:55</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">AASU Demands Strict Action After Assam Vehicles Targeted in Shillong Protest </t>
+          <t xml:space="preserve">Assam’s Indigenous ‘Asomi’ Sheep Breed Secures National Recognition from ICAR-NBAGR </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/topheadlines/aasu-demands-strict-action-after-assam-vehicles-targeted-in-shillong-protest</t>
+          <t>https://www.sentinelassam.com/topheadlines/assams-indigenous-asomi-sheep-breed-secures-national-recognition-from-icar-nbagr</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3803,7 +3803,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 03:54</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Assam (General)</t>
+          <t>Kamrup Metro</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Assam: Draft Electoral Roll Published for 35-Dihing Sessa Constituency</t>
+          <t xml:space="preserve">Guwahati: Two cops injured as dispute over land of ex-CM Mahanta turns violent; 8 held </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+          <t>https://www.sentinelassam.com/cities/guwahati-city/guwahati-two-cops-injured-as-dispute-over-land-of-ex-cm-mahanta-turns-violent-8-held</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 03:51</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Dibrugarh</t>
+          <t>Kamrup Metro</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Assam: Dibrugarh District Primary Teachers’ Association Extends Aid to Flood-Affected Schools</t>
+          <t xml:space="preserve">NDRF rescues 57-year-old woman from Brahmaputra in Guwahati </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Flood</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+          <t>https://www.sentinelassam.com/cities/guwahati-city/ndrf-rescues-57-year-old-woman-from-brahmaputra-in-guwahati</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3897,7 +3897,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 03:40</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Assam: AGP leader urges review of proposed Rakhyasini reserve forest boundary</t>
+          <t xml:space="preserve">Assam Government tightens rules for suspended employees </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+          <t>https://www.sentinelassam.com/topheadlines/assam-government-tightens-rules-for-suspended-employees</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 03:34</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Irrigation schemes fail in Barkhetri and Tihu; parched farmlands leave farmers worried</t>
+          <t xml:space="preserve">PM Modi Assures Unwavering Support as Assam CM Sarma Discusses Flood and Development Roadmap </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+          <t>https://www.sentinelassam.com/topheadlines/pm-modi-assures-unwavering-support-as-assam-cm-sarma-discusses-flood-and-development-roadmap</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3991,7 +3991,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 03:29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bodoland Lottery Results – 20th August, 2026: Complete List of Winners and Ticket Numbers</t>
+          <t xml:space="preserve">Meghalaya CM Sangma Holds Talks With Assam Counterpart to Restore Normalcy </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+          <t>https://www.sentinelassam.com/topheadlines/meghalaya-cm-sangma-holds-talks-with-assam-counterpart-to-restore-normalcy</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4038,7 +4038,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 03:24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Kamrup</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kamrup District Planning Committee Clears 2025-26 Annual Action Plan Under 15th Finance Commission</t>
+          <t xml:space="preserve">Assam-Meghalaya border tense at Jorabat amid blockade over alleged attacks on vehicles </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+          <t>https://www.sentinelassam.com/topheadlines/assam-meghalaya-border-tense-at-jorabat-amid-blockade-over-alleged-attacks-on-vehicles</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4085,7 +4085,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-21 10:25</t>
+          <t>2026-08-21 03:19</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Assam: Wildlife conservation meet in Raikona highlights need for human-elephant coexistence</t>
+          <t xml:space="preserve">AASU Demands Strict Action After Assam Vehicles Targeted in Shillong Protest </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+          <t>https://www.sentinelassam.com/topheadlines/aasu-demands-strict-action-after-assam-vehicles-targeted-in-shillong-protest</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tinsukia</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Assam: Draft Electoral Roll for MAC Election Published in Tinsukia District</t>
+          <t>Assam: Draft Electoral Roll Published for 35-Dihing Sessa Constituency</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Assam (General)</t>
+          <t>Dibrugarh</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Spate of Cattle Thefts in Sootea’s Nagsankar Area as Four Heads Worth Over Rs 2 Lakh Stolen</t>
+          <t>Assam: Dibrugarh District Primary Teachers’ Association Extends Aid to Flood-Affected Schools</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Assam: Special Workshop held in Agoratoli Range of Kaziranga National Park</t>
+          <t>Assam: AGP leader urges review of proposed Rakhyasini reserve forest boundary</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rangia Man Arrested for Allegedly Stabbing Wife to Death Amid Marital Dispute</t>
+          <t>Irrigation schemes fail in Barkhetri and Tihu; parched farmlands leave farmers worried</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Transgender woman found murdered in Rangia, live-in partner surrenders to police</t>
+          <t>Bodoland Lottery Results – 20th August, 2026: Complete List of Winners and Ticket Numbers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Kokrajhar</t>
+          <t>Kamrup</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Assam: 26th death anniversary of Subungthini Thandwi Bineswar Brahma observed in Kokrajhar</t>
+          <t>Kamrup District Planning Committee Clears 2025-26 Annual Action Plan Under 15th Finance Commission</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Assam: Minister Pijush Hazarika reviews agriculture &amp; irrigation schemes in Diphu</t>
+          <t>Assam: Wildlife conservation meet in Raikona highlights need for human-elephant coexistence</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Assam (General)</t>
+          <t>Tinsukia</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Assam: Draft Electoral Roll for 26-Buruli MAC Constituency Published with 7,349 Electors</t>
+          <t>Assam: Draft Electoral Roll for MAC Election Published in Tinsukia District</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Doomdooma Lekhika Samaroh Samiti holds monthly meet, highlights cultural significance of Sawan</t>
+          <t>Spate of Cattle Thefts in Sootea’s Nagsankar Area as Four Heads Worth Over Rs 2 Lakh Stolen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4555,814 +4555,814 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Assam: Special Workshop held in Agoratoli Range of Kaziranga National Park</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Rangia Man Arrested for Allegedly Stabbing Wife to Death Amid Marital Dispute</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Transgender woman found murdered in Rangia, live-in partner surrenders to police</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Kokrajhar</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Assam: 26th death anniversary of Subungthini Thandwi Bineswar Brahma observed in Kokrajhar</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Assam: Minister Pijush Hazarika reviews agriculture &amp; irrigation schemes in Diphu</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Assam: Draft Electoral Roll for 26-Buruli MAC Constituency Published with 7,349 Electors</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Doomdooma Lekhika Samaroh Samiti holds monthly meet, highlights cultural significance of Sawan</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>2026-08-21 04:35</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>Mizoram: Five held for transporting 45 African Swine Fever-infected pigs from Assam 
 Aizawl: Five people were arrested in Mizoram’s Mamit district after they were allegedly caught transporting 45 pigs infected with African Swine Fever (ASF) from Assam in violation of restrictions, an official of the State Animal Husbandry and Veterinary Department said on Thursday. The pigs were being transported in five vehicles for slaughter and sale in […]
 The post Mizoram: Five held for transporting 45 African Swine Fever-infected pigs from Assam appeared first on NorthEast Now.</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>https://nenow.in/north-east-news/mizoram/mizoram-five-held-for-transporting-45-african-swine-fever-infected-pigs-from-assam.html</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>2026-08-21 03:29</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t xml:space="preserve">Manipur: KNO, UPF reject SoO violation charges, reiterate demand for separate administration 
 Imphal: The Kuki National Organisation (KNO) and the United People’s Front (UPF), which represent 25 underground groups and around 2,200 cadres under the tripartite Suspension of Operations (SoO) agreement, have rejected allegations of violations of the ground rules governing the ceasefire framework. In a response to the Joint Monitoring Group (JMG), the two umbrella organisations […]
 The post Manipur: KNO, UPF reject SoO violation charges, reiterate demand for separate administration appeared first </t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>https://nenow.in/north-east-news/manipur/manipur-kno-upf-reject-soo-violation-charges-reiterate-demand-for-separate-administration.html</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>2026-08-21 02:36</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>Nagaland: ECI secretary Binod Kumar reviews SIR exercise in Kohima 
 Dimapur: Election Commission of India Secretary Binod Kumar on Thursday reviewed the progress of the Special Intensive Revision (SIR) exercise in Nagaland’s Kohima district. Addressing a review meeting at the Kohima DC’s office, Kumar urged officials to give their best and take the exercise seriously, stating that the SIR would have a generational impact on […]
 The post Nagaland: ECI secretary Binod Kumar reviews SIR exercise in Kohima appeared first on NorthEast Now.</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>https://nenow.in/north-east-news/nagaland/nagaland-eci-secretary-binod-kumar-reviews-sir-exercise-in-kohima.html</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>2026-08-21 02:06</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Kamrup Metro</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Mizoram’s lone medical college performs first successful open-heart surgery 
 Aizawl: Doctors at the state-run Zoram Medical College and Hospital (ZMC&amp;H) have performed Mizoram’s first open-heart surgery at the state’s lone medical college, hospital officials said on Thursday. A team led by resident cardiothoracic surgeon Mary Hmingthantluangi and Intekhab Alam from Apollo Excel Hospital in Guwahati performed coronary artery bypass grafting (CABG) on a 69-year-old […]
 The post Mizoram’s lone medical college performs first successful open-heart surgery appeared first on NorthEast Now.</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>https://nenow.in/north-east-news/mizoram/mizorams-lone-medical-college-performs-first-successful-open-heart-surgery.html</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>2026-08-21 01:44</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>Nagaland: MP S Supongmeren Jamir urges departmental heads to remain accessible to public 
 Dimapur: Nagaland’s lone Lok Sabha MP, S Supongmeren Jamir, on Thursday called upon all departmental heads to remain accessible and responsive to the needs of the public. He also called upon officers to ensure that the authority entrusted to them is not misused but exercised responsibly and in the larger interest of the district. Chairing […]
 The post Nagaland: MP S Supongmeren Jamir urges departmental heads to remain accessible to public appeared first on NorthEast Now.</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>https://nenow.in/north-east-news/nagaland/nagaland-mp-s-supongmeren-jamir-urges-departmental-heads-to-remain-accessible-to-public.html</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>2026-08-21 01:00</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
         <is>
           <t>Horoscope today, August 21, 2026: Check your astrological predictions here 
 Horoscope Today | August 21, 2026: If you are interested in astrology, let us take you through what your day could look like.    Here is the horoscope for August 21, 2026. Read what the stars have in store for you today (August 21,2026) Aries: Money matters could cause you some concern. You normally know where every penny has gone, but […]
 The post Horoscope today, August 21, 2026: Check your astrological predictions here appeared first on NorthEast Now.</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>https://nenow.in/lifestyle/horoscope-today-august-21-2026-check-your-astrological-predictions-here.html</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>2026-08-20 18:30</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>Manipur: Security forces arrest three in alleged drug, militant and extortion cases 
 Imphal: Security forces in Manipur carried out a series of operations across Imphal East, Imphal West and Bishnupur districts, arresting three individuals allegedly involved in drug smuggling, militant activities and extortion, and recovering suspected narcotics and a vehicle. According to Manipur Police reports on Thursday, the arrests and seizure took place over the past three […]
 The post Manipur: Security forces arrest three in alleged drug, militant and extortion cases appeared first on NorthEast Now.</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>https://nenow.in/north-east-news/manipur/manipur-security-forces-arrest-three-in-alleged-drug-militant-and-extortion-cases.html</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>2026-08-20 18:19</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>Cachar</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>Manipur: NH-37 vehicle movement resumes after transporters call off strike 
 Imphal: Vehicle movement along NH-37, the Imphal-Silchar route through Jiribam, resumed on August 20 after the Transporters’ and Drivers’ Council (TDC) withdrew its strike following assurances from the state government and security agencies. TDC president Hijam Ranjit said the decision was taken after a meeting on August 19 with the Chief Minister, Director General of […]
 The post Manipur: NH-37 vehicle movement resumes after transporters call off strike appeared first on NorthEast Now.</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>https://nenow.in/north-east-news/manipur/manipur-nh-37-vehicle-movement-resumes-after-transporters-call-off-strike.html</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>2026-08-20 17:56</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>Kamrup Metro</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Assam CM receives 120-year-old Kamakhya Devalaya land record dating to 1904-05 
 Guwahati: A land record dating back to 1904-05 belonging to the Kamakhya Devalaya was presented to Assam Chief Minister Himanta Biswa Sarma on August 19 during the inauguration of the Integrated District Commissioner’s Office in Guwahati. The century-old document is the Jamabandi of La-Kheraj Patta No. 1, covering Kamakhya Pahar revenue village under Ramsa Rani […]
 The post Assam CM receives 120-year-old Kamakhya Devalaya land record dating to 1904-05 appeared first on NorthEast Now.</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>https://nenow.in/north-east-news/assam/assam-cm-receives-120-year-old-kamakhya-devalaya-land-record-dating-to-1904-05.html</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>2026-08-20 17:31</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
         <is>
           <t>Manipur: Students push for NRC before Census, CM assures Assembly discussion 
 Imphal: Chief Minister Yumnam Khemchand Singh assured student representatives on August 20 that the state government supports the implementation of the National Register of Citizens (NRC) in Manipur. He said the issue would be discussed during the State Assembly session beginning on September 2. He also said that conducting the process and ensuring its error-free […]
 The post Manipur: Students push for NRC before Census, CM assures Assembly discussion appeared first on NorthEast Now.</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>https://nenow.in/north-east-news/manipur/manipur-students-push-for-nrc-before-census-cm-assures-assembly-discussion.html</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Northeast Now</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Assam CM receives 120-year-old Kamakhya Devalaya land record dating to 1904-05</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>https://nenow.in/north-east-news/assam/</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Northeast Now</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>CPI(M) to hold ‘Demand Day’ on August 21, seeks national disaster tag for Assam floods</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Flood</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>https://nenow.in/north-east-news/assam/</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Northeast Now</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Shillong rally violence: Assam, Meghalaya CMs call for peace, dialogue; ministers to meet</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>https://nenow.in/north-east-news/assam/</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Northeast Now</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Kamrup Metro</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Assam: Eight arrested in Guwahati’s Hatigaon over alleged attack on police personnel</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>https://nenow.in/north-east-news/assam/</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Northeast Now</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Former Mizoram CM Zoramthanga delivers lecture on insurgency at Gauhati University, receives degree certificate</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>https://nenow.in/north-east-news/assam/</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Northeast Now</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Assam Government plans 800 km rural road expansion under Rs 10,000-crore Asom Mala 4.0</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>https://nenow.in/north-east-news/assam/</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Northeast Now</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Assam: ED summons ACS officer Paragmoni Mahanta over alleged Rs 100 crore irregularities</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>https://nenow.in/north-east-news/assam/</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Assam: Meghalaya-registered vehicles reportedly stopped at Jorabat amid border tension</t>
+          <t>Assam CM receives 120-year-old Kamakhya Devalaya land record dating to 1904-05</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Assam family attacked, child injured during KSU rally violence in Shillong</t>
+          <t>CPI(M) to hold ‘Demand Day’ on August 21, seeks national disaster tag for Assam floods</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Jorhat</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Assam: Fourth accused Ankit Das arrested in Jorhat woman’s mysterious death case</t>
+          <t>Shillong rally violence: Assam, Meghalaya CMs call for peace, dialogue; ministers to meet</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5515,422 +5515,422 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Northeast Now</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Kamrup Metro</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Assam: Eight arrested in Guwahati’s Hatigaon over alleged attack on police personnel</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://nenow.in/north-east-news/assam/</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Northeast Now</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Former Mizoram CM Zoramthanga delivers lecture on insurgency at Gauhati University, receives degree certificate</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://nenow.in/north-east-news/assam/</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Northeast Now</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Assam Government plans 800 km rural road expansion under Rs 10,000-crore Asom Mala 4.0</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://nenow.in/north-east-news/assam/</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Northeast Now</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Assam: ED summons ACS officer Paragmoni Mahanta over alleged Rs 100 crore irregularities</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://nenow.in/north-east-news/assam/</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Northeast Now</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Assam: Meghalaya-registered vehicles reportedly stopped at Jorabat amid border tension</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://nenow.in/north-east-news/assam/</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Northeast Now</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Assam family attacked, child injured during KSU rally violence in Shillong</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://nenow.in/north-east-news/assam/</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Northeast Now</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Jorhat</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Assam: Fourth accused Ankit Das arrested in Jorhat woman’s mysterious death case</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://nenow.in/north-east-news/assam/</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>2026-08-20 15:56</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
         <is>
           <t>East Mojo</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
         <is>
           <t>Meghalaya, Assam CMs agree to work together to restore peace after Shillong violence 
 Shillong: Meghalaya Chief Minister Conrad K. Sangma, on Thursday spoke with Assam Chief Minister Dr. Himanta Biswa Sarma regarding the violence in Shillong on August 19 and the reactions that have followed, affecting common people and commuters in both states. Taking to X, Sangma said the two states had agreed to work together to normalise […]
 The post Meghalaya, Assam CMs agree to work together to restore peace after Shillong violence appeared first on EastMojo.</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>https://eastmojo.com/assam/2026/08/20/meghalaya-assam-cms-agree-to-work-together-to-restore-peace-after-shillong-violence/</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>2026-08-20 10:30</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>East Mojo</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
         <is>
           <t>Rupsi: History, erasure and the making of a borderland 
 Located in the western borderlands of the northeast Indian state of Assam, Rupsi is today known for its airport, popularly known as Rupsi Airport. However, the history of Rupsi has been shaped by colonial interests, wherein it served as a military airfield during the Second World War, transnational logistics, and postcolonial state formation. Today, Rupsi […]
 The post Rupsi: History, erasure and the making of a borderland appeared first on EastMojo.</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>https://eastmojo.com/premium/2026/08/20/rupsi-history-erasure-and-the-making-of-a-borderland/</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>East Mojo</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Meghalaya, Assam CMs agree to work together to restore peace after Shillong violence</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>https://www.eastmojo.com/assam/</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>East Mojo</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Rupsi: History, erasure and the making of a borderland</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>https://www.eastmojo.com/assam/</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>East Mojo</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>‘Andaman-endemic’ plant found in Assam, first mainland India record</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>https://www.eastmojo.com/assam/</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>East Mojo</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Long before modern conservation, India was studying elephants</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Elephant</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>https://www.eastmojo.com/assam/</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>East Mojo</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Tinsukia</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Assam: Three pilgrims drown in Kaliyapani river in Tinsukia</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>https://www.eastmojo.com/assam/</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>East Mojo</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Sivasagar</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Assam floods: Bal Raksha Bharat opens child-friendly space in Sivasagar</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Flood</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>https://www.eastmojo.com/assam/</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:25</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>East Mojo</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Small growers, rural women entrepreneurs take tea to new audiences at BIOFACH India</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>https://www.eastmojo.com/assam/</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>When a village decided its school could not wait</t>
+          <t>Meghalaya, Assam CMs agree to work together to restore peace after Shillong violence</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Kamrup Metro</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Jewellery worth Rs 40 lakh, cash burgled from Guwahati home</t>
+          <t>Rupsi: History, erasure and the making of a borderland</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>What happens when a Volleyball enters a prison in Assam?</t>
+          <t>‘Andaman-endemic’ plant found in Assam, first mainland India record</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6083,7 +6083,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-21 03:34</t>
+          <t>2026-08-21 10:25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Morung Express</t>
+          <t>East Mojo</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PM Modi extends birthday wishes to Arunachal CM Pema Khandu, hails his development initiatives New Delhi, August 21 (IANS) Prime Minister Narendra Modi on Friday extended birthday greetings to Arunachal Pradesh Chief Minister Pema Khandu, praising his efforts towards the development and progress of the northeastern state.Taking to X, PM Modi said Khandu was “at the forefront” of several initiatives aimed at taking Arunachal Pradesh to new heights of progress and wished him a long and healthy life in service of the people.“My best wishes to Arunachal Pradesh's Chief Minister, Shri Pema Khandu J</t>
+          <t>Long before modern conservation, India was studying elephants</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/pm-modi-extends-birthday-wishes-to-arunachal-cm-pema-khandu-hails-his-development-initiatives</t>
+          <t>https://www.eastmojo.com/assam/</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6130,7 +6130,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-20 16:38</t>
+          <t>2026-08-21 10:25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Morung Express</t>
+          <t>East Mojo</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Charaideo</t>
+          <t>Tinsukia</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mon police busts drug trafficking network 800 gm heroin, 6 arrestsMorung Express NewsDimapur | August 20The Mon police have claimed to have wrecked a drug supply chain following what it labelled as the “biggest anti-drug operation so far.” “Mon Police has successfully busted an inter-state drug trafficking network and seized approximately 800 grams of heroin, locally referred to as ‘Shan Flower,” stated a press release by the Mon police on August 20.&amp;nbsp;The arrests operation over three days, on August 19 and 20, conducted in coordination with the Charaideo police in Sonari, and the Dimapur p</t>
+          <t>Assam: Three pilgrims drown in Kaliyapani river in Tinsukia</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/mon-police-busts-drug-trafficking-network</t>
+          <t>https://www.eastmojo.com/assam/</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6177,7 +6177,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-20 16:30</t>
+          <t>2026-08-21 10:25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6187,17 +6187,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Morung Express</t>
+          <t>East Mojo</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Assam (General)</t>
+          <t>Sivasagar</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>NSF to hold 2-day national seminar on BEFR in Dimapur Dimapur, August 20 (MExN): The Naga Students’ Federation (NSF), through its Inner Line Regulation Commission (ILRC), will organise a two-day national seminar on the Bengal Eastern Frontier Regulation (BEFR), 1873, at Town Hall, Dimapur, on August 28 and 29. The seminar is being organised by the ILRC-NSF under the theme of ‘strengthening awareness and implementation of the BEFR, 1873.’According to the NSF, the seminar is intended as a national-level policy consultation to strengthen implementation of the BEFR, 1873, and consolidate recommend</t>
+          <t>Assam floods: Bal Raksha Bharat opens child-friendly space in Sivasagar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/nsf-to-hold-2-day-national-seminar-on-befr-in-dimapur</t>
+          <t>https://www.eastmojo.com/assam/</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6224,7 +6224,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-20 16:28</t>
+          <t>2026-08-21 10:25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6234,17 +6234,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Morung Express</t>
+          <t>East Mojo</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Kamrup Metro</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>NFR cancels, reschedules several trains MALIGAON, AUGUST 20 (MExN): The Northeast Frontier Railway (NFR) has announced changes to train services in view of ongoing restoration work near New Harangajao station in the Lumding–Badarpur Hill Section. The changes follow the settlement of railway tracks on Line-1 and Line-2. Train operations in the section are currently being maintained through Line-3 with enhanced safety measures, NFR stated in a release on Thursday.Train No. 15615 Guwahati–Silchar Express, scheduled to commence its journey on August 21, and Train No. 15616 Silchar–Guwahati Express</t>
+          <t>Small growers, rural women entrepreneurs take tea to new audiences at BIOFACH India</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Weather</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/nfr-cancels-reschedules-several-trains</t>
+          <t>https://www.eastmojo.com/assam/</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6271,7 +6271,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-20 16:18</t>
+          <t>2026-08-21 10:25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6281,17 +6281,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Morung Express</t>
+          <t>East Mojo</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Kamrup Metro</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Assam, Meghalaya CMs agree on joint efforts for peace after Shillong violence Guwahati, August 20 (IANS): Assam Chief Minister Himanta Biswa Sarma and his Meghalaya counterpart, Conrad K. Sangma, on Thursday spoke about the recent violence in Shillong and its fallout, agreeing to work together to restore peace, trust and normalcy between the two neighbouring states.Sangma said he spoke with Sarma regarding the violence that occurred in Shillong on August 19 and the reactions that followed, which have affected common people and commuters in both Assam and Meghalaya.“We have agreed to work toget</t>
+          <t>When a village decided its school could not wait</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Weather</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/assam-meghalaya-cms-agree-on-joint-efforts-for-peace-after-shillong-violence-1</t>
+          <t>https://www.eastmojo.com/assam/</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6318,7 +6318,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-20 15:56</t>
+          <t>2026-08-21 10:25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6328,17 +6328,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Morung Express</t>
+          <t>East Mojo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Assam (General)</t>
+          <t>Kamrup Metro</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Niketu Iralu’s legacy of healing and forgiveness honoured Morung Express NewsKohima | August 20Nagaland Chief Minister Dr Neiphiu Rio described Niketu Iralu as “one of Nagaland’s finest minds” and a person deeply committed to peace, reconciliation and social change.Dr Rio said Iralu’s passing following a brief illness in New Delhi was a loss not only to his family and the Naga people, but also to people around the world who knew and valued him.He briefly highlighted Niketu’s work with Moral Re-Armament, now known as Initiatives of Change, saying it reflected his lifelong belief in dialogue, un</t>
+          <t>Jewellery worth Rs 40 lakh, cash burgled from Guwahati home</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/niketu-iralus-legacy-of-healing-and-forgiveness-honoured</t>
+          <t>https://www.eastmojo.com/assam/</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6365,7 +6365,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-20 15:53</t>
+          <t>2026-08-21 10:25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6375,17 +6375,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Morung Express</t>
+          <t>East Mojo</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Kamrup Metro</t>
+          <t>Assam (General)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Assam, Meghalaya CMs agree on joint efforts for peace after Shillong violence Guwahati, August 20 (IANS) Assam Chief Minister Himanta Biswa Sarma and his Meghalaya counterpart, Conrad K. Sangma, on Thursday spoke about the recent violence in Shillong and its fallout, agreeing to work together to restore peace, trust and normalcy between the two neighbouring states.Sangma said he spoke with Sarma regarding the violence that occurred in Shillong on August 19 and the reactions that followed, which have affected common people and commuters in both Assam and Meghalaya.“We have agreed to work togeth</t>
+          <t>What happens when a Volleyball enters a prison in Assam?</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Weather</t>
+          <t>General</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/assam-meghalaya-cms-agree-on-joint-efforts-for-peace-after-shillong-violence</t>
+          <t>https://www.eastmojo.com/assam/</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6412,7 +6412,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-20 15:50</t>
+          <t>2026-08-21 03:34</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>A ‘Towering Moral Voice’: Tributes pour in for Niketu Iralu Dimapur, August 20 (MExN): A cross-section of Naga organisations, church bodies, political leaders, civil society groups and individuals have mourned the death of veteran peacebuilder, social worker and thinker Niketu Iralu, describing him as a moral voice who devoted his life to peace, reconciliation, dialogue and human dignity.Iralu, who died in New Delhi on August 18, was widely remembered for his decades-long efforts to bridge political, ethnic and social differences and promote non-violence and reconciliation.BWA: The Baptist Wor</t>
+          <t>PM Modi extends birthday wishes to Arunachal CM Pema Khandu, hails his development initiatives New Delhi, August 21 (IANS) Prime Minister Narendra Modi on Friday extended birthday greetings to Arunachal Pradesh Chief Minister Pema Khandu, praising his efforts towards the development and progress of the northeastern state.Taking to X, PM Modi said Khandu was “at the forefront” of several initiatives aimed at taking Arunachal Pradesh to new heights of progress and wished him a long and healthy life in service of the people.“My best wishes to Arunachal Pradesh's Chief Minister, Shri Pema Khandu J</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/a-towering-moral-voice-tributes-pour-in-for-niketu-iralu</t>
+          <t>https://morungexpress.com/pm-modi-extends-birthday-wishes-to-arunachal-cm-pema-khandu-hails-his-development-initiatives</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6459,623 +6459,1712 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>2026-08-20 16:38</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Morung Express</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Charaideo</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Mon police busts drug trafficking network 800 gm heroin, 6 arrestsMorung Express NewsDimapur | August 20The Mon police have claimed to have wrecked a drug supply chain following what it labelled as the “biggest anti-drug operation so far.” “Mon Police has successfully busted an inter-state drug trafficking network and seized approximately 800 grams of heroin, locally referred to as ‘Shan Flower,” stated a press release by the Mon police on August 20.&amp;nbsp;The arrests operation over three days, on August 19 and 20, conducted in coordination with the Charaideo police in Sonari, and the Dimapur p</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://morungexpress.com/mon-police-busts-drug-trafficking-network</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:30</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Morung Express</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>NSF to hold 2-day national seminar on BEFR in Dimapur Dimapur, August 20 (MExN): The Naga Students’ Federation (NSF), through its Inner Line Regulation Commission (ILRC), will organise a two-day national seminar on the Bengal Eastern Frontier Regulation (BEFR), 1873, at Town Hall, Dimapur, on August 28 and 29. The seminar is being organised by the ILRC-NSF under the theme of ‘strengthening awareness and implementation of the BEFR, 1873.’According to the NSF, the seminar is intended as a national-level policy consultation to strengthen implementation of the BEFR, 1873, and consolidate recommend</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://morungexpress.com/nsf-to-hold-2-day-national-seminar-on-befr-in-dimapur</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:28</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Morung Express</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Kamrup Metro</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>NFR cancels, reschedules several trains MALIGAON, AUGUST 20 (MExN): The Northeast Frontier Railway (NFR) has announced changes to train services in view of ongoing restoration work near New Harangajao station in the Lumding–Badarpur Hill Section. The changes follow the settlement of railway tracks on Line-1 and Line-2. Train operations in the section are currently being maintained through Line-3 with enhanced safety measures, NFR stated in a release on Thursday.Train No. 15615 Guwahati–Silchar Express, scheduled to commence its journey on August 21, and Train No. 15616 Silchar–Guwahati Express</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://morungexpress.com/nfr-cancels-reschedules-several-trains</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:18</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Morung Express</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Kamrup Metro</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Assam, Meghalaya CMs agree on joint efforts for peace after Shillong violence Guwahati, August 20 (IANS): Assam Chief Minister Himanta Biswa Sarma and his Meghalaya counterpart, Conrad K. Sangma, on Thursday spoke about the recent violence in Shillong and its fallout, agreeing to work together to restore peace, trust and normalcy between the two neighbouring states.Sangma said he spoke with Sarma regarding the violence that occurred in Shillong on August 19 and the reactions that followed, which have affected common people and commuters in both Assam and Meghalaya.“We have agreed to work toget</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://morungexpress.com/assam-meghalaya-cms-agree-on-joint-efforts-for-peace-after-shillong-violence-1</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:56</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Morung Express</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Niketu Iralu’s legacy of healing and forgiveness honoured Morung Express NewsKohima | August 20Nagaland Chief Minister Dr Neiphiu Rio described Niketu Iralu as “one of Nagaland’s finest minds” and a person deeply committed to peace, reconciliation and social change.Dr Rio said Iralu’s passing following a brief illness in New Delhi was a loss not only to his family and the Naga people, but also to people around the world who knew and valued him.He briefly highlighted Niketu’s work with Moral Re-Armament, now known as Initiatives of Change, saying it reflected his lifelong belief in dialogue, un</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://morungexpress.com/niketu-iralus-legacy-of-healing-and-forgiveness-honoured</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:53</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Morung Express</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Kamrup Metro</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Assam, Meghalaya CMs agree on joint efforts for peace after Shillong violence Guwahati, August 20 (IANS) Assam Chief Minister Himanta Biswa Sarma and his Meghalaya counterpart, Conrad K. Sangma, on Thursday spoke about the recent violence in Shillong and its fallout, agreeing to work together to restore peace, trust and normalcy between the two neighbouring states.Sangma said he spoke with Sarma regarding the violence that occurred in Shillong on August 19 and the reactions that followed, which have affected common people and commuters in both Assam and Meghalaya.“We have agreed to work togeth</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://morungexpress.com/assam-meghalaya-cms-agree-on-joint-efforts-for-peace-after-shillong-violence</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:50</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Morung Express</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>A ‘Towering Moral Voice’: Tributes pour in for Niketu Iralu Dimapur, August 20 (MExN): A cross-section of Naga organisations, church bodies, political leaders, civil society groups and individuals have mourned the death of veteran peacebuilder, social worker and thinker Niketu Iralu, describing him as a moral voice who devoted his life to peace, reconciliation, dialogue and human dignity.Iralu, who died in New Delhi on August 18, was widely remembered for his decades-long efforts to bridge political, ethnic and social differences and promote non-violence and reconciliation.BWA: The Baptist Wor</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://morungexpress.com/a-towering-moral-voice-tributes-pour-in-for-niketu-iralu</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
           <t>2026-08-21 02:36</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>Northeast Today</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
         <is>
           <t>Tripura: BJP Moves to Break Deadlock with Tipra Motha Party Ahead of Village Committee Polls Agartala, August 21, 2026: With the implementation of the tripartite agreement emerging as a major point of contention between the BJP and its ally Tipra Motha, senior leaders of the two parties are set to hold discussions in Agartala on Friday ahead of the elections to the ADC Village Committees. The meeting is expected to...
 The post Tripura: BJP Moves to Break Deadlock with Tipra Motha Party Ahead of Village Committee Polls first appeared on Northeast Today.</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>https://northeasttoday.in/northeast/tripura-bjp-moves-to-break-deadlock-with-tipra-motha-party-ahead-of-village-committee-polls/</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I136" t="inlineStr">
         <is>
           <t>2026-08-21 10:26</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>2026-08-20 19:14</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
         <is>
           <t>Northeast Today</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
         <is>
           <t>Tripura CM Dr Manik Saha Calls for Greater Opportunities for Women’s Education, Skills and Economic Self-Reliance Agartala, August 21, 2026: Tripura Chief Minister Professor (Dr.) Manik Saha on Thursday stressed the need for expanding opportunities for women’s education, skill development and economic self-reliance alongside ensuring their safety and protection. The Chief Minister made the remarks while presiding over two consecutive meetings at Conference Hall No. 1 of the Secretariat—one with the...
 The post Tripura CM Dr Manik Saha Calls for Greater Opportunities for Women’s Education, Skil</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>https://northeasttoday.in/northeast/tripura-cm-dr-manik-saha-calls-for-greater-opportunities-for-womens-education-skills-and-economic-self-reliance/</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>2026-08-21 10:26</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>2026-08-20 19:14</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
         <is>
           <t>Northeast Today</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
         <is>
           <t xml:space="preserve">Tripura Governor Calls for Scientific Approach to Make Pig Farming Profitable; Minister Sudhangshu Das Urges Farmers to Adopt Modern Methods Agartala, August 21, 2026: Tripura Governor Indrasena Reddy Nallu on Thursday emphasized the important role of pig farming in strengthening Tripura’s rural economy, urging farmers to adopt modern technologies and scientific practices to improve productivity and income. The Governor inaugurated a seminar and workshop on modern pig farming methods at Pragya Bhavan and visited exhibition...
 The post Tripura Governor Calls for Scientific Approach to Make Pig </t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>https://northeasttoday.in/northeast/tripura-governor-calls-for-scientific-approach-to-make-pig-farming-profitable-minister-sudhangshu-das-urges-farmers-to-adopt-modern-methods/</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I138" t="inlineStr">
         <is>
           <t>2026-08-21 10:26</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>2026-08-20 16:34</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
         <is>
           <t>Northeast Today</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
         <is>
           <t>Manipur MP Bimol Akoijam Urges Centre To Halt Census, Cites Lack Of Credible Conditions Congress MP from Inner Manipur Angomcha Bimol Akoijam has urged the Centre to defer the ongoing Census in Manipur and any subsequent delimitation exercise until conditions are conducive to a credible and inclusive enumeration. In a letter to Union Home Minister Amit Shah dated August 19, Akoijam recalled his intervention in the Lok Sabha under...
 The post Manipur MP Bimol Akoijam Urges Centre To Halt Census, Cites Lack Of Credible Conditions first appeared on Northeast Today.</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>https://northeasttoday.in/northeast/manipur-mp-bimol-akoijam-urges-centre-to-halt-census-cites-lack-of-credible-conditions/</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t>2026-08-21 10:26</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>2026-08-20 16:31</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
         <is>
           <t>Northeast Today</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
         <is>
           <t xml:space="preserve">“We Agreed To Work Together To Normalise Situation”: Meghalaya CM Conrad Sangma After Talk With Assam CM Following Shillong Violence Shillong, August 20: Meghalaya Chief Minister Conrad K. Sangma on Thursday spoke with Assam Chief Minister Himanta Biswa Sarma over the violence reported in Shillong and the tensions that followed along the Assam-Meghalaya border. The two chief ministers agreed to coordinate efforts to restore peace and normalcy, with designated Cabinet ministers from both states expected...
 The post “We Agreed To Work Together To Normalise Situation”: Meghalaya CM Conrad Sangma </t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>https://northeasttoday.in/northeast/we-agreed-to-work-together-to-normalise-situation-meghalaya-cm-conrad-sangma-after-talk-with-assam-cm-following-shillong-violence/</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t>2026-08-21 10:26</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>2026-08-20 16:26</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
         <is>
           <t>Northeast Today</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
         <is>
           <t xml:space="preserve">“Arunachal Is Not A Political Battleground”: Congress’  Byaling Seeks Independent Probe Into Taksing Border Allegations, Rejects Rijiju’s Remarks Itanagar, August 20: Former Home Minister and APCC Working President Tanga Byaling on Thursday rejected remarks made by Union Minister and Arunachal MP Kiren Rijiju in response to LoP Rahul Gandhi’s concerns over alleged Chinese activities along the Arunachal border. Byaling said national security must not be turned into a BJP vs Congress debate. “The...
 The post “Arunachal Is Not A Political Battleground”: Congress’  Byaling Seeks Independent Probe </t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>https://northeasttoday.in/uncategorized/arunachal-is-not-a-political-battleground-congress-byaling-seeks-independent-probe-into-taksing-border-allegations-rejects-rijijus-remarks/</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t>2026-08-21 10:26</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>2026-08-20 16:19</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
         <is>
           <t>Northeast Today</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
         <is>
           <t>132 kV Along-Kambang Transmission Line Charged In Arunachal; DCM Calls It Investment In West Siang’s Future Itanagar, August 20: The successful charging of the 132 kV Along–Kambang Transmission Line and the 132/33 kV Kambang Substation has been hailed as a major infrastructure milestone that will strengthen power supply in West Siang and surrounding districts. Deputy Chief Minister Chowna Mein said the project is “more than an infrastructure milestone, it is an...
 The post 132 kV Along-Kambang Transmission Line Charged In Arunachal; DCM Calls It Investment In West Siang’s Future first appeared</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>https://northeasttoday.in/northeast/arunachal-pradesh/132-kv-along-kambang-transmission-line-charged-in-arunachal-dcm-calls-it-investment-in-west-siangs-future/</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t>2026-08-21 10:26</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>2026-08-20 14:31</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
         <is>
           <t>Northeast Today</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
         <is>
           <t>Tripura: Surrendered Militants Submit Nine-Point Charter to Governor, Warn of Larger Agitation Agartala, August 20, 2026: A delegation representing the Joint Action Rehabilitation Committee (JARC) and Joint Action Committee (JAC) of surrendered militants on Thursday met Governor Indrasena Reddy Nallu at Lok Bhavan and submitted a memorandum containing a nine-point charter of demands. The development comes days after a road blockade by a group of surrendered militants...
 The post Tripura: Surrendered Militants Submit Nine-Point Charter to Governor, Warn of Larger Agitation first appeared on Nor</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>https://northeasttoday.in/northeast/tripura-surrendered-militants-submit-nine-point-charter-to-governor-warn-of-larger-agitation/</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>2026-08-21 10:26</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>2026-08-20 13:50</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>Northeast Today</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
         <is>
           <t>Centre Approves Deployment Of Five Companies Of Central Forces In Meghalaya After Shillong Violence Shillong, Aug 20: The Union Home Ministry has sanctioned the deployment of five companies of central forces in Meghalaya following violent protests in Shillong that left several people injured, vehicles damaged, and a government car set ablaze. Officials confirmed that four companies of the Central Reserve Police Force (CRPF) and one company of the Rapid...
 The post Centre Approves Deployment Of Five Companies Of Central Forces In Meghalaya After Shillong Violence first appeared on Northeast Tod</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>https://northeasttoday.in/northeast/centre-approves-deployment-of-five-companies-of-central-forces-in-meghalaya-after-shillong-violence/</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t>2026-08-21 10:26</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>2026-08-20 13:22</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
         <is>
           <t>Northeast Today</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
         <is>
           <t>Education, Tourism, Startups Top Agenda as NITI Aayog Member Dr. Joram Aniya Meets Tripura CM Dr. Manik Saha Agartala, August 20, 2026: Dr. Joram Aniya, Member of NITI Aayog, met Tripura Chief Minister Dr. Manik Saha during her visit to the state, accompanied by senior officials of NITI Aayog, to discuss key development priorities and areas of collaboration between the state government and the policy think tank. The discussions identified school education, tourism,...
 The post Education, Tourism, Startups Top Agenda as NITI Aayog Member Dr. Joram Aniya Meets Tripura CM Dr. Manik Saha first app</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="H145" t="inlineStr">
         <is>
           <t>https://northeasttoday.in/northeast/education-tourism-startups-top-agenda-as-niti-aayog-member-dr-joram-aniya-meets-tripura-cm-dr-manik-saha/</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="I145" t="inlineStr">
         <is>
           <t>2026-08-21 10:26</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>2026-08-21 04:44</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
         <is>
           <t>The Sentinel Assam</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>Kamrup Metro</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t xml:space="preserve">Meghalaya Taxi Association Suspends Shillong-Guwahati Services </t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>https://www.sentinelassam.com/breakingnews/meghalaya-taxi-association-suspends-shillong-guwahati-services</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I146" t="inlineStr">
         <is>
           <t>2026-08-21 10:33</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>2026-08-21 04:31</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>The Sentinel Assam</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Assam (General)</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
         <is>
           <t xml:space="preserve">BJP slams Shillong protest violence, urges Meghalaya to protect Assam tourists and taxi drivers </t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>https://www.sentinelassam.com/cities/guwahati-city/bjp-slams-shillong-protest-violence-urges-meghalaya-to-protect-assam-tourists-and-taxi-drivers</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="I147" t="inlineStr">
         <is>
           <t>2026-08-21 10:33</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>2026-08-21 04:59</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>News Website</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>Northeast Now</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>Kamrup Metro</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>Meghalaya taxi drivers suspend Shillong-Guwahati services 
 Guwahati: The Meghalaya taxi drivers’ association has announced the suspension of commercial taxi services between Shillong and Guwahati following recent violence in Shillong, including the alleged attack on tourists from Assam during the Khasi Students’ Union (KSU) black-flag motorcycle rally. The association has also warned that taxi services from Assam to Meghalaya could be suspended […]
 The post Meghalaya taxi drivers suspend Shillong-Guwahati services appeared first on NorthEast Now.</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>https://nenow.in/north-east-news/meghalaya/meghalaya-taxi-drivers-suspend-shillong-guwahati-services.html</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t>2026-08-21 10:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-21 07:25</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assam Premier League unveils Rs 50 lakh prize for champions, Rs 25 lakh for runners-up </t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/sports-news/local-sports/assam-premier-league-unveils-rs-50-lakh-prize-for-champions-rs-25-lakh-for-runners-up</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-21 07:20</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assam Premier League 2026: Dibrugarh Warriors edge past Nagaon Rangers </t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/sports-news/local-sports/assam-premier-league-2026-dibrugarh-warriors-edge-past-nagaon-rangers</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-21 07:15</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assam Premier League 2026: Sibsankar Roy leads Barak Legends to easy victory </t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/sports-news/local-sports/assam-premier-league-2026-sibsankar-roy-leads-barak-legends-to-easy-victory</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-21 06:10</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assam Floods: Gaurav Gogoi Questions PM CARES Fund, Demands Rs 10,000 Crore Special Package </t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Flood</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/breakingnews/assam-floods-gaurav-gogoi-questions-pm-cares-fund-demands-rs-10000-crore-special-package</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Darrang</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Assam: Teaching paralysed in Darrang schools due to mismanagement of Census duty</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Assam: Debabrata Saikia slams government over compensation for flood victims</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Flood</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Kokrajhar</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Assam: Demonstration on enhancing productivity of Muga and Eri held in Kokrajhar</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Assam: Two dumpers carrying illegal stone and sand seized in Numaligarh</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>The Sentinel Assam</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Assam entrepreneur Tushar Tayal selected for G20 YEA Summit in Vienna</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://www.sentinelassam.com/north-east-india-news/assam-news/</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:03</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>East Mojo</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Kamrup Metro</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Manipur: Bus service to Guwahati resumes after 3 years 
+Imphal: As part of the State Government’s continuing efforts to restore peace and normalcy, public transport services on the Imphal–Dimapur–Guwahati route resumed on Friday, marking a significant development after a gap of nearly three years since the unprecedented crisis in the state.  A total of 125 passengers travelled on the route, in two buses and […]
+The post Manipur: Bus service to Guwahati resumes after 3 years appeared first on EastMojo.</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://eastmojo.com/manipur/2026/08/21/manipur-bus-service-to-guwahati-resumes-after-3-years/</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:02</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Northeast Today</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Tripura Govt Will Bear 100% Burden of Tariff Hike: Minister Ratan Lal Nath Announces Full Relief for Power Consumers Agartala, August 21, 2026: Tripura Power Minister Ratan Lal Nath on Friday announced that the state government will bear the entire burden of the additional electricity charges imposed under the Tripura Electricity Regulatory Commission’s (TERC) tariff order for 2026-27 through a 100 per cent subsidy. Addressing a press conference, Nath said the decision was taken...
+The post Tripura Govt Will Bear 100% Burden of Tariff Hike: Minister Ratan Lal Nath Announces Full Relief for Pow</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://northeasttoday.in/northeast/tripura-govt-will-bear-100-burden-of-tariff-hike-minister-ratan-lal-nath-announces-full-relief-for-power-consumers/</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-21 07:13</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Northeast Today</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Manipur: Arms Cache Recovered Along Indo-Myanmar Border In Moreh A joint team of Moreh Police Station and the 36 Assam Rifles recovered a concealed cache of arms, ammunition and explosives from a forested area along the Indo-Myanmar border in Manipur’s Moreh on Thursday. Acting on specific intelligence inputs, the joint team launched an operation in the general area of Border Pillar (BP) 73 on...
+The post Manipur: Arms Cache Recovered Along Indo-Myanmar Border In Moreh first appeared on Northeast Today.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://northeasttoday.in/northeast/manipur-arms-cache-recovered-along-indo-myanmar-border-in-moreh/</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-21 07:03</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Northeast Today</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Arunachal: 25 Farmers In Kyidphel Circle Get Horticulture Support Under Vibrant Villages Programme In a step towards strengthening border area livelihoods, 25 farmers from Kyidphel Block, Tawang District received horticultural inputs under the Vibrant Villages Programme (VVP) of the Ministry of Home Affairs. An awareness-cum-input distribution event was held in Kyidphel Circle this month to promote organic farming and sustainable vegetable cultivation through the Mission for Integrated Development...
+The post Arunachal: 25 Farmers In Kyidphel Circle Get Horticulture Support Under Vibrant Villa</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://northeasttoday.in/uncategorized/arunachal-25-farmers-in-kyidphel-circle-get-horticulture-support-under-vibrant-villages-programme/</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-21 06:06</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Northeast Today</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Arunachal: Governor KT Parnaik Inaugurates Broadcast &amp; Digital Media Resource Centre At RGU Governor of Arunachal Pradesh Lt Gen (Retd) KT Parnaik inaugurated the state-of-the-art Broadcast &amp; Digital Media Resource Centre at Rajiv Gandhi University (RGU) in Rono Hills. The new facility, established at the Department of Mass Communication, is aimed at transforming media education in the state by equipping students with high-tech infrastructure for modern audio-visual training...
+The post Arunachal: Governor KT Parnaik Inaugurates Broadcast &amp; Digital Media Resource Centre At RGU first appeared o</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://northeasttoday.in/northeast/arunachal-pradesh/arunachal-governor-kt-parnaik-inaugurates-broadcast-digital-media-resource-centre-at-rgu/</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-21 05:42</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Northeast Today</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Gaurav Gogoi Writes To PM Modi, Seeks Rs 10,000 Crore Special Package For Flood-Hit Assam Congress leader Gaurav Gogoi has appealed to Prime Minister Narendra Modi to sanction a special relief package of ₹10,000 crore for Assam in the wake of the devastating floods that struck the state. Gogoi, who serves as the Deputy Leader of Opposition in the Lok Sabha and also heads the Assam Congress, emphasized that the...
+The post Gaurav Gogoi Writes To PM Modi, Seeks Rs 10,000 Crore Special Package For Flood-Hit Assam first appeared on Northeast Today.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Flood</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://northeasttoday.in/northeast/assam/gaurav-gogoi-writes-to-pm-modi-seeks-rs-10000-crore-special-package-for-flood-hit-assam/</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-21 05:41</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>News Website</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Northeast Today</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Assam (General)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Tripura: Three Detained With 9.42 Grams of Heroin in Kakraban; Family Alleges False Charges Agartala, August 21, 2026: Acting on a tip-off, police from Kakraban Police Station detained three youths and allegedly recovered 9.42 grams of heroin from their possession during an operation in the Hadra-Samatal Para area on Friday evening. According to police, the operation was conducted at around 8 pm. The three youths were detained along with...
+The post Tripura: Three Detained With 9.42 Grams of Heroin in Kakraban; Family Alleges False Charges first appeared on Northeast Today.</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://northeasttoday.in/northeast/tripura-three-detained-with-9-42-grams-of-heroin-in-kakraban-family-alleges-false-charges/</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:35</t>
         </is>
       </c>
     </row>
